--- a/SFMO/NERIS Tech Rescue Incident Types.xlsx
+++ b/SFMO/NERIS Tech Rescue Incident Types.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ddion\Python Scripts\neris-toolbox\SFMO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA0E5A57-9B96-4CE1-B40B-C39BD5739C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{745A39C9-3BE3-43E6-88F5-DB13D439F429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F54C2FAA-4B81-4E1A-B602-CD8B3D27F58E}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="59">
   <si>
     <t>PUBSERV||CITIZEN_ASSIST||OBSTRUCTION_DEBRIS</t>
   </si>
@@ -656,6 +656,9 @@
       <c r="B2" t="s">
         <v>28</v>
       </c>
+      <c r="C2" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
